--- a/KandRStyle/research/risk_air_gap/ComputerCrime_AMERICAN_SAMOA_JUL2026.xlsx
+++ b/KandRStyle/research/risk_air_gap/ComputerCrime_AMERICAN_SAMOA_JUL2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gladi\source\repos\bookWork2\KandRStyle\research\risk_air_gap\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B1C6736-8FC4-4564-BC03-44B16A4B5596}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0CB80F7A-8FD6-422B-8B83-AD13E54BA283}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="4" xr2:uid="{A6B90A6B-86D8-4A34-B9C9-776670F3C0EC}"/>
   </bookViews>

--- a/KandRStyle/research/risk_air_gap/ComputerCrime_AMERICAN_SAMOA_JUL2026.xlsx
+++ b/KandRStyle/research/risk_air_gap/ComputerCrime_AMERICAN_SAMOA_JUL2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gladi\source\repos\bookWork2\KandRStyle\research\risk_air_gap\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0CB80F7A-8FD6-422B-8B83-AD13E54BA283}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4448AED3-1690-4B7A-9336-031770E983C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="4" xr2:uid="{A6B90A6B-86D8-4A34-B9C9-776670F3C0EC}"/>
   </bookViews>
